--- a/school_counselor_forms/008_return_to_school_survey--school_counselor_forms.xlsx
+++ b/school_counselor_forms/008_return_to_school_survey--school_counselor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -782,7 +782,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Will child attend tomorrow</t>
+          <t>Will Child Attend Tomorrow Tomorrow</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Will child attend school tomorrow</t>
+          <t>Will Child Attend School Tomorrow Tomorrow Tomorrow</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Will child attend tomorrow</t>
+          <t>Will Child Attend Tomorrow Tomorrow Tomorrow</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -869,12 +869,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>will_child_attend_school_tomorrow_tomorrow_tomorrow</t>
+          <t>will_child_attend_school_tomorrow_tomorrow_tomorrow_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Will child attend school tomorrow</t>
+          <t>Will Child Attend School Tomorrow Tomorrow Tomorrow 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Will child attend tomorrow</t>
+          <t>Will Child Attend Tomorrow Tomorrow Tomorrow Tomorrow</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>School name</t>
+          <t>School Name School</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Contact number</t>
+          <t>Contact Number Contact Number</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Email</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1344,7 +1344,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>will_child_attend_school_tomorrow_tomorrow_tomorrow_choices</t>
+          <t>will_child_attend_school_tomorrow_tomorrow_tomorrow_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1361,7 +1361,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>will_child_attend_school_tomorrow_tomorrow_tomorrow_choices</t>
+          <t>will_child_attend_school_tomorrow_tomorrow_tomorrow_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1378,7 +1378,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>will_child_attend_school_tomorrow_tomorrow_tomorrow_choices</t>
+          <t>will_child_attend_school_tomorrow_tomorrow_tomorrow_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
